--- a/outputs/Third trial/05_RGB_Growth_Rate_Treatment_Comparison/_reports/rgb_growth_treatment_report.xlsx
+++ b/outputs/Third trial/05_RGB_Growth_Rate_Treatment_Comparison/_reports/rgb_growth_treatment_report.xlsx
@@ -11,20 +11,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tray Daily Metrics" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Group Daily Metrics" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Group Growth Metrics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day7 Imputed Cells" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heat Phase Response" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moisture Phase Response" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inside Outside Compare" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day7 Imputed Cells" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heat Phase Response" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moisture Phase Response" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tray Growth Metrics'!$A$1:$AW$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tray Daily Metrics'!$A$1:$AD$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Group Daily Metrics'!$A$1:$O$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Group Growth Metrics'!$A$1:$AE$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Day7 Imputed Cells'!$A$1:$BN$199</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Heat Phase Response'!$A$1:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Moisture Phase Response'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Read Me'!$A$1:$A$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Inside Outside Compare'!$A$1:$X$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Day7 Imputed Cells'!$A$1:$BN$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Heat Phase Response'!$A$1:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Moisture Phase Response'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Read Me'!$A$1:$A$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5147,7 +5149,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>No Microbes</t>
+          <t>Microbes</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -5173,19 +5175,19 @@
         <v>4.2857</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>2.0203</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.0037</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.0057</v>
+        <v>0.0007</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.0037</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.0057</v>
+        <v>0.0007</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>3</v>
@@ -5202,7 +5204,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>No Microbes</t>
+          <t>Microbes</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -5225,25 +5227,25 @@
         <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>91.4286</v>
+        <v>70.71429999999999</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>2.0203</v>
+        <v>13.132</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.7613</v>
+        <v>0.5036</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0184</v>
+        <v>0.163</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.7613</v>
+        <v>0.5036</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.0184</v>
+        <v>0.163</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>61</v>
+        <v>46.5</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>0</v>
@@ -5257,7 +5259,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>No Microbes</t>
+          <t>Microbes</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -5280,25 +5282,25 @@
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>93.5714</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>1.0102</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.5448</v>
+        <v>1.3519</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.042</v>
+        <v>0.1599</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.5448</v>
+        <v>1.3519</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.042</v>
+        <v>0.1599</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>0</v>
@@ -5312,7 +5314,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>No Microbes</t>
+          <t>Microbes</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -5335,25 +5337,25 @@
         <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>97.1429</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1.0102</v>
+        <v>2.0203</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>2.6309</v>
+        <v>2.5826</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.3289</v>
+        <v>0.3465</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>2.6309</v>
+        <v>2.5826</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3289</v>
+        <v>0.3465</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>0</v>
@@ -5367,7 +5369,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>No Microbes</t>
+          <t>Microbes</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -5390,22 +5392,22 @@
         <v>2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>97.1429</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.0102</v>
+        <v>2.0203</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>3.1786</v>
+        <v>3.2425</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.3527</v>
+        <v>0.2226</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>3.1786</v>
+        <v>3.2425</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.3527</v>
+        <v>0.2226</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
@@ -5422,7 +5424,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>No Microbes</t>
+          <t>Microbes</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -5445,25 +5447,25 @@
         <v>2</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.5714</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.0102</v>
+        <v>2.0203</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.6815</v>
+        <v>4.5033</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.3327</v>
+        <v>0.6401</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2.6815</v>
+        <v>4.5033</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.3327</v>
+        <v>0.6401</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>0</v>
@@ -5477,7 +5479,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>No Microbes</t>
+          <t>Microbes</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -5500,28 +5502,28 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.5714</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1.0102</v>
+        <v>2.0203</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>3.2063</v>
+        <v>6.6041</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.5198</v>
+        <v>0.7863</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>4.3828</v>
+        <v>6.7916</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.5767</v>
+        <v>0.5211</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -5532,7 +5534,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Microbes</t>
+          <t>No Microbes</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -5558,19 +5560,19 @@
         <v>4.2857</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>2.0203</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.0037</v>
+        <v>0.0055</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.0007</v>
+        <v>0.0057</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.0037</v>
+        <v>0.0055</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.0007</v>
+        <v>0.0057</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>3</v>
@@ -5587,7 +5589,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Microbes</t>
+          <t>No Microbes</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -5610,25 +5612,25 @@
         <v>2</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>70.71429999999999</v>
+        <v>91.4286</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>13.132</v>
+        <v>2.0203</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.5036</v>
+        <v>0.7613</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.163</v>
+        <v>0.0184</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.5036</v>
+        <v>0.7613</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.163</v>
+        <v>0.0184</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>46.5</v>
+        <v>61</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0</v>
@@ -5642,7 +5644,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Microbes</t>
+          <t>No Microbes</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -5665,25 +5667,25 @@
         <v>2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>93.5714</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>1.0102</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.3519</v>
+        <v>1.5448</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.1599</v>
+        <v>0.042</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1.3519</v>
+        <v>1.5448</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.1599</v>
+        <v>0.042</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>16</v>
+        <v>5.5</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>0</v>
@@ -5697,7 +5699,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Microbes</t>
+          <t>No Microbes</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -5720,25 +5722,25 @@
         <v>2</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>97.1429</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.0102</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.5826</v>
+        <v>2.6309</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.3465</v>
+        <v>0.3289</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2.5826</v>
+        <v>2.6309</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.3465</v>
+        <v>0.3289</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -5752,7 +5754,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Microbes</t>
+          <t>No Microbes</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -5775,22 +5777,22 @@
         <v>2</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>97.1429</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.0102</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>3.2425</v>
+        <v>3.1786</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.2226</v>
+        <v>0.3527</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>3.2425</v>
+        <v>3.1786</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.2226</v>
+        <v>0.3527</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>0</v>
@@ -5807,7 +5809,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Microbes</t>
+          <t>No Microbes</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -5830,25 +5832,25 @@
         <v>2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>98.5714</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.0102</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>4.5033</v>
+        <v>2.6815</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.6401</v>
+        <v>0.3327</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>4.5033</v>
+        <v>2.6815</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.6401</v>
+        <v>0.3327</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>0</v>
@@ -5862,7 +5864,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Microbes</t>
+          <t>No Microbes</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -5885,28 +5887,28 @@
         <v>2</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>98.5714</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.0102</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>6.6041</v>
+        <v>3.2063</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.7863</v>
+        <v>0.5198</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>6.7916</v>
+        <v>4.3828</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.5211</v>
+        <v>0.5767</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
@@ -5917,7 +5919,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Dynamic Heat</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
@@ -5937,25 +5939,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>4.2857</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>1.1664</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.0037</v>
+        <v>0.0046</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.0007</v>
+        <v>0.0035</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.0037</v>
+        <v>0.0046</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.0007</v>
+        <v>0.0035</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>3</v>
@@ -5965,14 +5967,14 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Treatment Type</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Dynamic Heat</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
@@ -5992,42 +5994,42 @@
         <v>1</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>70.71429999999999</v>
+        <v>81.0714</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>13.132</v>
+        <v>14.2081</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.5036</v>
+        <v>0.6325</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.163</v>
+        <v>0.1764</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.5036</v>
+        <v>0.6325</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.163</v>
+        <v>0.1764</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>46.5</v>
+        <v>53.75</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Treatment Type</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Dynamic Heat</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -6047,42 +6049,42 @@
         <v>2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>93.5714</v>
+        <v>96.4286</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>1.0102</v>
+        <v>3.4007</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.3519</v>
+        <v>1.4483</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.1599</v>
+        <v>0.1467</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.3519</v>
+        <v>1.4483</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.1599</v>
+        <v>0.1467</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>16</v>
+        <v>10.75</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Treatment Type</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Dynamic Heat</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
@@ -6102,42 +6104,42 @@
         <v>3</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>97.1429</v>
+        <v>98.21429999999999</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.7976</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>2.5826</v>
+        <v>2.6067</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.3465</v>
+        <v>0.2772</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2.5826</v>
+        <v>2.6067</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.3465</v>
+        <v>0.2772</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Treatment Type</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Dynamic Heat</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -6157,25 +6159,25 @@
         <v>4</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>97.1429</v>
+        <v>98.21429999999999</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.7976</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.2425</v>
+        <v>3.2105</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2226</v>
+        <v>0.2436</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>3.2425</v>
+        <v>3.2105</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.2226</v>
+        <v>0.2436</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0</v>
@@ -6185,14 +6187,14 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Treatment Type</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Dynamic Heat</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -6212,42 +6214,42 @@
         <v>5</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>98.5714</v>
+        <v>98.9286</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.3678</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>4.5033</v>
+        <v>3.5924</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.6401</v>
+        <v>1.1313</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>4.5033</v>
+        <v>3.5924</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.6401</v>
+        <v>1.1313</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Treatment Type</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Dynamic Heat</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -6267,42 +6269,42 @@
         <v>8</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>98.5714</v>
+        <v>98.9286</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.3678</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>6.6041</v>
+        <v>4.9052</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.7863</v>
+        <v>2.0358</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>6.7916</v>
+        <v>5.5872</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.5211</v>
+        <v>1.4613</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Treatment Type</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Dynamic Heat</t>
+          <t>Microbes | Heat</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -6328,19 +6330,19 @@
         <v>4.2857</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.0203</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.0037</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.0057</v>
+        <v>0.0007</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.0037</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.0057</v>
+        <v>0.0007</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>3</v>
@@ -6350,14 +6352,14 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Microbe x Treatment</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Dynamic Heat</t>
+          <t>Microbes | Heat</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -6380,39 +6382,39 @@
         <v>2</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>91.4286</v>
+        <v>70.71429999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2.0203</v>
+        <v>13.132</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.7613</v>
+        <v>0.5036</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.0184</v>
+        <v>0.163</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.7613</v>
+        <v>0.5036</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.0184</v>
+        <v>0.163</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>61</v>
+        <v>46.5</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Microbe x Treatment</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Dynamic Heat</t>
+          <t>Microbes | Heat</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -6435,39 +6437,39 @@
         <v>2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>93.5714</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>1.0102</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1.5448</v>
+        <v>1.3519</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.042</v>
+        <v>0.1599</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1.5448</v>
+        <v>1.3519</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.042</v>
+        <v>0.1599</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Microbe x Treatment</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Dynamic Heat</t>
+          <t>Microbes | Heat</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
@@ -6490,39 +6492,39 @@
         <v>2</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>97.1429</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.0102</v>
+        <v>2.0203</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.6309</v>
+        <v>2.5826</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.3289</v>
+        <v>0.3465</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.6309</v>
+        <v>2.5826</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.3289</v>
+        <v>0.3465</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Microbe x Treatment</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Dynamic Heat</t>
+          <t>Microbes | Heat</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -6545,22 +6547,22 @@
         <v>2</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>97.1429</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.0102</v>
+        <v>2.0203</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.1786</v>
+        <v>3.2425</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.3527</v>
+        <v>0.2226</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3.1786</v>
+        <v>3.2425</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.3527</v>
+        <v>0.2226</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>0</v>
@@ -6570,14 +6572,14 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Microbe x Treatment</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Dynamic Heat</t>
+          <t>Microbes | Heat</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
@@ -6600,39 +6602,39 @@
         <v>2</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.5714</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1.0102</v>
+        <v>2.0203</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.6815</v>
+        <v>4.5033</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.3327</v>
+        <v>0.6401</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>2.6815</v>
+        <v>4.5033</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.3327</v>
+        <v>0.6401</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Microbe x Treatment</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Dynamic Heat</t>
+          <t>Microbes | Heat</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -6655,39 +6657,39 @@
         <v>2</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.5714</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.0102</v>
+        <v>2.0203</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.2063</v>
+        <v>6.6041</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.5198</v>
+        <v>0.7863</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>4.3828</v>
+        <v>6.7916</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.5767</v>
+        <v>0.5211</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Microbe x Treatment</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Heat</t>
+          <t>No Microbes | Heat</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -6713,19 +6715,19 @@
         <v>4.2857</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0</v>
+        <v>2.0203</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.0037</v>
+        <v>0.0055</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.0007</v>
+        <v>0.0057</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.0037</v>
+        <v>0.0055</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.0007</v>
+        <v>0.0057</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>3</v>
@@ -6742,7 +6744,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Heat</t>
+          <t>No Microbes | Heat</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -6765,25 +6767,25 @@
         <v>2</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>70.71429999999999</v>
+        <v>91.4286</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>13.132</v>
+        <v>2.0203</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.5036</v>
+        <v>0.7613</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.163</v>
+        <v>0.0184</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.5036</v>
+        <v>0.7613</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.163</v>
+        <v>0.0184</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>46.5</v>
+        <v>61</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0</v>
@@ -6797,7 +6799,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Heat</t>
+          <t>No Microbes | Heat</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -6820,25 +6822,25 @@
         <v>2</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>93.5714</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>1.0102</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.3519</v>
+        <v>1.5448</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.1599</v>
+        <v>0.042</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1.3519</v>
+        <v>1.5448</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1599</v>
+        <v>0.042</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>16</v>
+        <v>5.5</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0</v>
@@ -6852,7 +6854,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Heat</t>
+          <t>No Microbes | Heat</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
@@ -6875,25 +6877,25 @@
         <v>2</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>97.1429</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.0102</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.5826</v>
+        <v>2.6309</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.3465</v>
+        <v>0.3289</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>2.5826</v>
+        <v>2.6309</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.3465</v>
+        <v>0.3289</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>0</v>
@@ -6907,7 +6909,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Heat</t>
+          <t>No Microbes | Heat</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
@@ -6930,22 +6932,22 @@
         <v>2</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>97.1429</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.0102</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>3.2425</v>
+        <v>3.1786</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.2226</v>
+        <v>0.3527</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>3.2425</v>
+        <v>3.1786</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.2226</v>
+        <v>0.3527</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0</v>
@@ -6962,7 +6964,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Heat</t>
+          <t>No Microbes | Heat</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
@@ -6985,25 +6987,25 @@
         <v>2</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>98.5714</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.0102</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>4.5033</v>
+        <v>2.6815</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.6401</v>
+        <v>0.3327</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>4.5033</v>
+        <v>2.6815</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.6401</v>
+        <v>0.3327</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>0</v>
@@ -7017,7 +7019,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Heat</t>
+          <t>No Microbes | Heat</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
@@ -7040,28 +7042,28 @@
         <v>2</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>98.5714</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.0102</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>6.6041</v>
+        <v>3.2063</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.7863</v>
+        <v>0.5198</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>6.7916</v>
+        <v>4.3828</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.5211</v>
+        <v>0.5767</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
@@ -7072,7 +7074,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Heat</t>
+          <t>Heat | Dynamic Heat</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
@@ -7092,25 +7094,25 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>4.2857</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.1664</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.0046</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.0057</v>
+        <v>0.0035</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0.0055</v>
+        <v>0.0046</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.0057</v>
+        <v>0.0035</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>3</v>
@@ -7120,14 +7122,14 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Treatment</t>
+          <t>Treatment x Environment</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Heat</t>
+          <t>Heat | Dynamic Heat</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
@@ -7147,42 +7149,42 @@
         <v>1</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>91.4286</v>
+        <v>81.0714</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2.0203</v>
+        <v>14.2081</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.7613</v>
+        <v>0.6325</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.0184</v>
+        <v>0.1764</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.7613</v>
+        <v>0.6325</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.0184</v>
+        <v>0.1764</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>61</v>
+        <v>53.75</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Treatment</t>
+          <t>Treatment x Environment</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Heat</t>
+          <t>Heat | Dynamic Heat</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
@@ -7202,42 +7204,42 @@
         <v>2</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>96.4286</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.0102</v>
+        <v>3.4007</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.5448</v>
+        <v>1.4483</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.042</v>
+        <v>0.1467</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.5448</v>
+        <v>1.4483</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.042</v>
+        <v>0.1467</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>5.5</v>
+        <v>10.75</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Treatment</t>
+          <t>Treatment x Environment</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Heat</t>
+          <t>Heat | Dynamic Heat</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
@@ -7257,42 +7259,42 @@
         <v>3</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.21429999999999</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>1.0102</v>
+        <v>1.7976</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.6309</v>
+        <v>2.6067</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.3289</v>
+        <v>0.2772</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>2.6309</v>
+        <v>2.6067</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.3289</v>
+        <v>0.2772</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Treatment</t>
+          <t>Treatment x Environment</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Heat</t>
+          <t>Heat | Dynamic Heat</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
@@ -7312,25 +7314,25 @@
         <v>4</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.21429999999999</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.0102</v>
+        <v>1.7976</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>3.1786</v>
+        <v>3.2105</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.3527</v>
+        <v>0.2436</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>3.1786</v>
+        <v>3.2105</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.3527</v>
+        <v>0.2436</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>0</v>
@@ -7340,14 +7342,14 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Treatment</t>
+          <t>Treatment x Environment</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Heat</t>
+          <t>Heat | Dynamic Heat</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
@@ -7367,42 +7369,42 @@
         <v>5</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.9286</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1.0102</v>
+        <v>1.3678</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.6815</v>
+        <v>3.5924</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.3327</v>
+        <v>1.1313</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>2.6815</v>
+        <v>3.5924</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.3327</v>
+        <v>1.1313</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Treatment</t>
+          <t>Treatment x Environment</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Heat</t>
+          <t>Heat | Dynamic Heat</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
@@ -7422,42 +7424,42 @@
         <v>8</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.9286</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>1.0102</v>
+        <v>1.3678</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>3.2063</v>
+        <v>4.9052</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.5198</v>
+        <v>2.0358</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>4.3828</v>
+        <v>5.5872</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.5767</v>
+        <v>1.4613</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Treatment</t>
+          <t>Treatment x Environment</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
@@ -7477,25 +7479,25 @@
         <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>4.2857</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>1.1664</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.0046</v>
+        <v>0.0037</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.0035</v>
+        <v>0.0007</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.0046</v>
+        <v>0.0037</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.0035</v>
+        <v>0.0007</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>3</v>
@@ -7505,14 +7507,14 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>Treatment Type</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
@@ -7532,42 +7534,42 @@
         <v>1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>81.0714</v>
+        <v>70.71429999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>14.2081</v>
+        <v>13.132</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.5036</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.1764</v>
+        <v>0.163</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.5036</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1764</v>
+        <v>0.163</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>53.75</v>
+        <v>46.5</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>Treatment Type</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
@@ -7587,42 +7589,42 @@
         <v>2</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>96.4286</v>
+        <v>93.5714</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>3.4007</v>
+        <v>1.0102</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>1.4483</v>
+        <v>1.3519</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.1467</v>
+        <v>0.1599</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.4483</v>
+        <v>1.3519</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1467</v>
+        <v>0.1599</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>10.75</v>
+        <v>16</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>Treatment Type</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
@@ -7642,42 +7644,42 @@
         <v>3</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>98.21429999999999</v>
+        <v>97.1429</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>1.7976</v>
+        <v>2.0203</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>2.6067</v>
+        <v>2.5826</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.2772</v>
+        <v>0.3465</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>2.6067</v>
+        <v>2.5826</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.2772</v>
+        <v>0.3465</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>Treatment Type</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
@@ -7697,25 +7699,25 @@
         <v>4</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>98.21429999999999</v>
+        <v>97.1429</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.7976</v>
+        <v>2.0203</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.2105</v>
+        <v>3.2425</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.2436</v>
+        <v>0.2226</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.2105</v>
+        <v>3.2425</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.2436</v>
+        <v>0.2226</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -7725,14 +7727,14 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>Treatment Type</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
@@ -7752,42 +7754,42 @@
         <v>5</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>98.9286</v>
+        <v>98.5714</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>1.3678</v>
+        <v>2.0203</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>3.5924</v>
+        <v>4.5033</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>1.1313</v>
+        <v>0.6401</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>3.5924</v>
+        <v>4.5033</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>1.1313</v>
+        <v>0.6401</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>Treatment Type</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
@@ -7807,42 +7809,42 @@
         <v>8</v>
       </c>
       <c r="F50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>98.5714</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>2.0203</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>6.6041</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0.7863</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>6.7916</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.5211</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G50" s="3" t="n">
-        <v>98.9286</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>1.3678</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>4.9052</v>
-      </c>
-      <c r="J50" s="3" t="n">
-        <v>2.0358</v>
-      </c>
-      <c r="K50" s="3" t="n">
-        <v>5.5872</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>1.4613</v>
-      </c>
-      <c r="M50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>Treatment Type</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Heat | Dynamic Heat</t>
+          <t>No Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
@@ -7862,25 +7864,25 @@
         <v>0</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>4.2857</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>1.1664</v>
+        <v>2.0203</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.0046</v>
+        <v>0.0055</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.0046</v>
+        <v>0.0055</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.0035</v>
+        <v>0.0057</v>
       </c>
       <c r="M51" s="3" t="n">
         <v>3</v>
@@ -7890,14 +7892,14 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>Treatment x Environment</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Heat | Dynamic Heat</t>
+          <t>No Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
@@ -7917,42 +7919,42 @@
         <v>1</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>81.0714</v>
+        <v>91.4286</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>14.2081</v>
+        <v>2.0203</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.7613</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.1764</v>
+        <v>0.0184</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>0.6325</v>
+        <v>0.7613</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1764</v>
+        <v>0.0184</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>53.75</v>
+        <v>61</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>Treatment x Environment</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Heat | Dynamic Heat</t>
+          <t>No Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
@@ -7972,42 +7974,42 @@
         <v>2</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>96.4286</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>3.4007</v>
+        <v>1.0102</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>1.4483</v>
+        <v>1.5448</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.1467</v>
+        <v>0.042</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>1.4483</v>
+        <v>1.5448</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1467</v>
+        <v>0.042</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>10.75</v>
+        <v>5.5</v>
       </c>
       <c r="N53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>Treatment x Environment</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Heat | Dynamic Heat</t>
+          <t>No Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
@@ -8027,42 +8029,42 @@
         <v>3</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>98.21429999999999</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>1.7976</v>
+        <v>1.0102</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2.6067</v>
+        <v>2.6309</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.2772</v>
+        <v>0.3289</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2.6067</v>
+        <v>2.6309</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.2772</v>
+        <v>0.3289</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>Treatment x Environment</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Heat | Dynamic Heat</t>
+          <t>No Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
@@ -8082,25 +8084,25 @@
         <v>4</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>98.21429999999999</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>1.7976</v>
+        <v>1.0102</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>3.2105</v>
+        <v>3.1786</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.2436</v>
+        <v>0.3527</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>3.2105</v>
+        <v>3.1786</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.2436</v>
+        <v>0.3527</v>
       </c>
       <c r="M55" s="3" t="n">
         <v>0</v>
@@ -8110,14 +8112,14 @@
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>Treatment x Environment</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Heat | Dynamic Heat</t>
+          <t>No Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
@@ -8137,42 +8139,42 @@
         <v>5</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>98.9286</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>1.3678</v>
+        <v>1.0102</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>3.5924</v>
+        <v>2.6815</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>1.1313</v>
+        <v>0.3327</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>3.5924</v>
+        <v>2.6815</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>1.1313</v>
+        <v>0.3327</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>Treatment x Environment</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Heat | Dynamic Heat</t>
+          <t>No Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
@@ -8192,35 +8194,35 @@
         <v>8</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>98.9286</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>1.3678</v>
+        <v>1.0102</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>4.9052</v>
+        <v>3.2063</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>2.0358</v>
+        <v>0.5198</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>5.5872</v>
+        <v>4.3828</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>1.4613</v>
+        <v>0.5767</v>
       </c>
       <c r="M57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>Treatment x Environment</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
@@ -8432,77 +8434,77 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>No Microbes</t>
+          <t>Microbes</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.5714</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.0102</v>
+        <v>2.0203</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3.2063</v>
+        <v>6.6041</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.5198</v>
+        <v>0.7863</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>4.3828</v>
+        <v>6.7916</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.5767</v>
+        <v>0.5211</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0</v>
+        <v>5.6569</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.1764</v>
+        <v>0.1875</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.0569</v>
+        <v>0.2652</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>11.875</v>
+        <v>11.7857</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.1263</v>
+        <v>0.2525</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.4001</v>
+        <v>0.825</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.0643</v>
+        <v>0.0982</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.5472</v>
+        <v>0.8485</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.175</v>
+        <v>0.7003</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>0.0624</v>
+        <v>0.0487</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.5671</v>
+        <v>0.7628</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>0.0814</v>
+        <v>0.0397</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.5246</v>
+        <v>0.7019</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>0.0232</v>
+        <v>0.1388</v>
       </c>
       <c r="Y2" s="3" t="n">
         <v>0</v>
@@ -8511,16 +8513,16 @@
         <v>0</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>52.2609</v>
+        <v>61.5786</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>6.3754</v>
+        <v>11.4967</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>53.9746</v>
+        <v>62.0983</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>8.7989</v>
+        <v>12.2316</v>
       </c>
       <c r="AE2" s="3" t="inlineStr">
         <is>
@@ -8531,77 +8533,77 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Microbes</t>
+          <t>No Microbes</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>98.5714</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.0102</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6.6041</v>
+        <v>3.2063</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.7863</v>
+        <v>0.5198</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6.7916</v>
+        <v>4.3828</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.5211</v>
+        <v>0.5767</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>5.6569</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.1875</v>
+        <v>1.1764</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2652</v>
+        <v>0.0569</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>11.7857</v>
+        <v>11.875</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>0.2525</v>
+        <v>0.1263</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>0.825</v>
+        <v>0.4001</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.0982</v>
+        <v>0.0643</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.8485</v>
+        <v>0.5472</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7003</v>
+        <v>0.175</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>0.0487</v>
+        <v>0.0624</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0.7628</v>
+        <v>0.5671</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0.0397</v>
+        <v>0.0814</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7019</v>
+        <v>0.5246</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>0.1388</v>
+        <v>0.0232</v>
       </c>
       <c r="Y3" s="3" t="n">
         <v>0</v>
@@ -8610,16 +8612,16 @@
         <v>0</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>61.5786</v>
+        <v>52.2609</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>11.4967</v>
+        <v>6.3754</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>62.0983</v>
+        <v>53.9746</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>12.2316</v>
+        <v>8.7989</v>
       </c>
       <c r="AE3" s="3" t="inlineStr">
         <is>
@@ -8630,77 +8632,77 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Dynamic Heat</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>98.5714</v>
+        <v>98.9286</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.3678</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>6.6041</v>
+        <v>4.9052</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.7863</v>
+        <v>2.0358</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6.7916</v>
+        <v>5.5872</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5211</v>
+        <v>1.4613</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>5.6569</v>
+        <v>8.7178</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.1875</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.2652</v>
+        <v>0.592</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>11.7857</v>
+        <v>11.8304</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.2525</v>
+        <v>0.171</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0.825</v>
+        <v>0.6126</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.0982</v>
+        <v>0.2545</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.8485</v>
+        <v>0.6978</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.1827</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7003</v>
+        <v>0.4376</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.0487</v>
+        <v>0.3067</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.7628</v>
+        <v>0.6649</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>0.0397</v>
+        <v>0.1245</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7019</v>
+        <v>0.6132</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>0.1388</v>
+        <v>0.1307</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
@@ -8709,97 +8711,97 @@
         <v>0</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>61.5786</v>
+        <v>56.9197</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>11.4967</v>
+        <v>9.303000000000001</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>62.0983</v>
+        <v>58.0364</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>12.2316</v>
+        <v>9.883100000000001</v>
       </c>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Treatment Type</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Dynamic Heat</t>
+          <t>Microbes | Heat</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.5714</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.0102</v>
+        <v>2.0203</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3.2063</v>
+        <v>6.6041</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.5198</v>
+        <v>0.7863</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4.3828</v>
+        <v>6.7916</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.5767</v>
+        <v>0.5211</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>5.6569</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.1764</v>
+        <v>0.1875</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.0569</v>
+        <v>0.2652</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>11.875</v>
+        <v>11.7857</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.1263</v>
+        <v>0.2525</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0.4001</v>
+        <v>0.825</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.0643</v>
+        <v>0.0982</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.5472</v>
+        <v>0.8485</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.175</v>
+        <v>0.7003</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.0624</v>
+        <v>0.0487</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.5671</v>
+        <v>0.7628</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0.0814</v>
+        <v>0.0397</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.5246</v>
+        <v>0.7019</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0.0232</v>
+        <v>0.1388</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>0</v>
@@ -8808,97 +8810,97 @@
         <v>0</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>52.2609</v>
+        <v>61.5786</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>6.3754</v>
+        <v>11.4967</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>53.9746</v>
+        <v>62.0983</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>8.7989</v>
+        <v>12.2316</v>
       </c>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Environment</t>
+          <t>Microbe x Treatment</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Microbes | Heat</t>
+          <t>No Microbes | Heat</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>98.5714</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.0203</v>
+        <v>1.0102</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6.6041</v>
+        <v>3.2063</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.7863</v>
+        <v>0.5198</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6.7916</v>
+        <v>4.3828</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.5211</v>
+        <v>0.5767</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5.6569</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1875</v>
+        <v>1.1764</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2652</v>
+        <v>0.0569</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>11.7857</v>
+        <v>11.875</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.2525</v>
+        <v>0.1263</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.825</v>
+        <v>0.4001</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.0982</v>
+        <v>0.0643</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.8485</v>
+        <v>0.5472</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7003</v>
+        <v>0.175</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.0487</v>
+        <v>0.0624</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.7628</v>
+        <v>0.5671</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.0397</v>
+        <v>0.0814</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7019</v>
+        <v>0.5246</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.1388</v>
+        <v>0.0232</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>0</v>
@@ -8907,16 +8909,16 @@
         <v>0</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>61.5786</v>
+        <v>52.2609</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>11.4967</v>
+        <v>6.3754</v>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>62.0983</v>
+        <v>53.9746</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>12.2316</v>
+        <v>8.7989</v>
       </c>
       <c r="AE6" s="3" t="inlineStr">
         <is>
@@ -8927,77 +8929,77 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>No Microbes | Heat</t>
+          <t>Heat | Dynamic Heat</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>99.28570000000001</v>
+        <v>98.9286</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.0102</v>
+        <v>1.3678</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3.2063</v>
+        <v>4.9052</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.5198</v>
+        <v>2.0358</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4.3828</v>
+        <v>5.5872</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.5767</v>
+        <v>1.4613</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>8.7178</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.1764</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.0569</v>
+        <v>0.592</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>11.875</v>
+        <v>11.8304</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.1263</v>
+        <v>0.171</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.4001</v>
+        <v>0.6126</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.0643</v>
+        <v>0.2545</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.5472</v>
+        <v>0.6978</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1827</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.175</v>
+        <v>0.4376</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>0.0624</v>
+        <v>0.3067</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>0.5671</v>
+        <v>0.6649</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>0.0814</v>
+        <v>0.1245</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.5246</v>
+        <v>0.6132</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>0.0232</v>
+        <v>0.1307</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>0</v>
@@ -9006,97 +9008,97 @@
         <v>0</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>52.2609</v>
+        <v>56.9197</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>6.3754</v>
+        <v>9.303000000000001</v>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>53.9746</v>
+        <v>58.0364</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>8.7989</v>
+        <v>9.883100000000001</v>
       </c>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>Microbe x Treatment</t>
+          <t>Treatment x Environment</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>98.5714</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2.0203</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>6.6041</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.7863</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>6.7916</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.5211</v>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>98.9286</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>1.3678</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>4.9052</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>2.0358</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>5.5872</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>1.4613</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="J8" s="3" t="n">
-        <v>8.7178</v>
+        <v>5.6569</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.1875</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.592</v>
+        <v>0.2652</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>11.8304</v>
+        <v>11.7857</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.171</v>
+        <v>0.2525</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.6126</v>
+        <v>0.825</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.2545</v>
+        <v>0.0982</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.6978</v>
+        <v>0.8485</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1827</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.4376</v>
+        <v>0.7003</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.3067</v>
+        <v>0.0487</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0.6649</v>
+        <v>0.7628</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>0.1245</v>
+        <v>0.0397</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6132</v>
+        <v>0.7019</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>0.1307</v>
+        <v>0.1388</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>0</v>
@@ -9105,97 +9107,97 @@
         <v>0</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>56.9197</v>
+        <v>61.5786</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>9.303000000000001</v>
+        <v>11.4967</v>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>58.0364</v>
+        <v>62.0983</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>9.883100000000001</v>
+        <v>12.2316</v>
       </c>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>Treatment Type</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Heat | Dynamic Heat</t>
+          <t>No Microbes | Dynamic Heat</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>98.9286</v>
+        <v>99.28570000000001</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.3678</v>
+        <v>1.0102</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>4.9052</v>
+        <v>3.2063</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2.0358</v>
+        <v>0.5198</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5.5872</v>
+        <v>4.3828</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.4613</v>
+        <v>0.5767</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>8.7178</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.6820000000000001</v>
+        <v>1.1764</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.592</v>
+        <v>0.0569</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>11.8304</v>
+        <v>11.875</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.171</v>
+        <v>0.1263</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0.6126</v>
+        <v>0.4001</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.2545</v>
+        <v>0.0643</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.6978</v>
+        <v>0.5472</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.1827</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.4376</v>
+        <v>0.175</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>0.3067</v>
+        <v>0.0624</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0.6649</v>
+        <v>0.5671</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>0.1245</v>
+        <v>0.0814</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6132</v>
+        <v>0.5246</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>0.1307</v>
+        <v>0.0232</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>0</v>
@@ -9204,20 +9206,20 @@
         <v>0</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>56.9197</v>
+        <v>52.2609</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>9.303000000000001</v>
+        <v>6.3754</v>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>58.0364</v>
+        <v>53.9746</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>9.883100000000001</v>
+        <v>8.7989</v>
       </c>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>Treatment x Environment</t>
+          <t>Microbe x Environment</t>
         </is>
       </c>
     </row>
@@ -9228,6 +9230,245 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="43" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="46" customWidth="1" min="21" max="21"/>
+    <col width="54" customWidth="1" min="22" max="22"/>
+    <col width="36" customWidth="1" min="23" max="23"/>
+    <col width="35" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>inside_tray_count</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>outside_tray_count</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>inside_trays</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>outside_trays</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>inside_final_emergence_percent</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>outside_final_emergence_percent</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>inside_final_observed_green_cover_percent</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>outside_final_observed_green_cover_percent</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>inside_final_adjusted_green_cover_percent</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>outside_final_adjusted_green_cover_percent</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>inside_emergence_rate_pp_per_day</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>outside_emergence_rate_pp_per_day</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>inside_adjusted_green_cover_rate_pp_per_day</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>outside_adjusted_green_cover_rate_pp_per_day</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>inside_t50_elapsed_days</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>outside_t50_elapsed_days</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>inside_overall_adjusted_rgb_score</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>outside_overall_adjusted_rgb_score</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>inside_minus_outside_final_emergence_pp</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>inside_minus_outside_adjusted_green_cover_pp</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>inside_minus_outside_adjusted_growth_rate_pp_per_day</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>inside_minus_outside_overall_score</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Ideal</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr"/>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>Insufficient data for comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Moisture</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Insufficient data for comparison.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62090,7 +62331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62701,7 +62942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62722,13 +62963,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -62758,7 +62999,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Adjusted Day 7 values are only created for cells that were visible before Day 7 but missing on Day 7.</t>
+          <t>Adjusted Day 7 values are created only for cells that were visible before Day 7 but missing on Day 7.</t>
         </is>
       </c>
     </row>
@@ -62786,19 +63027,26 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>This is descriptive image-derived analysis, not formal statistical proof.</t>
+          <t>The Inside vs Outside sheet compares only Ideal and Moisture trays because Heat trays had dynamic movement.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>These are descriptive image-derived results, not formal statistical proof.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>NDVI/NDRE are not included here; they are handled by later multispectral scripts.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A9"/>
+  <autoFilter ref="A1:A10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>